--- a/data/trans_orig/P2C_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34804</t>
+          <t>35461</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43321</t>
+          <t>43207</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37776</t>
+          <t>38621</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46871</t>
+          <t>47043</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>76386</t>
+          <t>76746</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>87847</t>
+          <t>88635</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>89,65%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4386</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12903</t>
+          <t>12246</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4293</t>
+          <t>4121</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13388</t>
+          <t>12543</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11024</t>
+          <t>10236</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22485</t>
+          <t>22125</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,38%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30654</t>
+          <t>30655</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43882</t>
+          <t>44092</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25557</t>
+          <t>25246</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38378</t>
+          <t>37952</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>58,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>60337</t>
+          <t>61237</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>78719</t>
+          <t>78776</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>59,31%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24005</t>
+          <t>23795</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>37233</t>
+          <t>37232</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26556</t>
+          <t>26982</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>39377</t>
+          <t>39688</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>54101</t>
+          <t>54044</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>72483</t>
+          <t>71583</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>53,89%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39333</t>
+          <t>38718</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51452</t>
+          <t>52020</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46323</t>
+          <t>46099</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56772</t>
+          <t>56776</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>89352</t>
+          <t>88566</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>105936</t>
+          <t>106161</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>80,06%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13245</t>
+          <t>12677</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25364</t>
+          <t>25979</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11130</t>
+          <t>11126</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21579</t>
+          <t>21803</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26664</t>
+          <t>26439</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>43248</t>
+          <t>44034</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>33,21%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47203</t>
+          <t>47059</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57671</t>
+          <t>56921</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53307</t>
+          <t>52515</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64033</t>
+          <t>63556</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>103480</t>
+          <t>101965</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>118353</t>
+          <t>118085</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,61%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8383</t>
+          <t>9133</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18851</t>
+          <t>18995</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9483</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20209</t>
+          <t>21001</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>21216</t>
+          <t>21484</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36089</t>
+          <t>37604</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>26,94%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4623</t>
+          <t>4643</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8834</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2755</t>
+          <t>2778</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8383</t>
+          <t>8305</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9148</t>
+          <t>9329</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16011</t>
+          <t>16413</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>78,38%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>706</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4918</t>
+          <t>4898</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3016</t>
+          <t>3094</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8644</t>
+          <t>8621</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4930</t>
+          <t>4528</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11793</t>
+          <t>11612</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>55,45%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26219</t>
+          <t>26326</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36493</t>
+          <t>36649</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29652</t>
+          <t>30708</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40388</t>
+          <t>41534</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>59675</t>
+          <t>59528</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>74331</t>
+          <t>74630</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>75,44%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10166</t>
+          <t>10010</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20440</t>
+          <t>20333</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11883</t>
+          <t>10737</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>22619</t>
+          <t>21563</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>24598</t>
+          <t>24299</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>39254</t>
+          <t>39401</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,83%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>79083</t>
+          <t>78993</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>93141</t>
+          <t>94377</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>67328</t>
+          <t>68541</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>83832</t>
+          <t>83055</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>153324</t>
+          <t>152910</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>173876</t>
+          <t>173395</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,31%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17505</t>
+          <t>16269</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>31563</t>
+          <t>31653</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>26954</t>
+          <t>27731</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>43458</t>
+          <t>42245</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>47557</t>
+          <t>48038</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>68109</t>
+          <t>68523</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,95%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>40745</t>
+          <t>39810</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>56241</t>
+          <t>55942</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>52451</t>
+          <t>52241</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>68210</t>
+          <t>67206</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>96657</t>
+          <t>97683</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>118049</t>
+          <t>119857</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>64,18%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>33926</t>
+          <t>34225</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>49422</t>
+          <t>50357</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>28367</t>
+          <t>29371</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>44126</t>
+          <t>44336</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>68696</t>
+          <t>66888</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>90088</t>
+          <t>89062</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>47,69%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>333400</t>
+          <t>334656</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>366650</t>
+          <t>367316</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>346609</t>
+          <t>346730</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>381488</t>
+          <t>380608</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>691673</t>
+          <t>689538</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>741191</t>
+          <t>738597</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,58%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>136709</t>
+          <t>136043</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>169959</t>
+          <t>168703</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>147061</t>
+          <t>147941</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>181940</t>
+          <t>181819</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>290717</t>
+          <t>293311</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>340235</t>
+          <t>342370</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,18%</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22042</t>
+          <t>21762</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34275</t>
+          <t>33760</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>58899</t>
+          <t>58663</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62925</t>
+          <t>62931</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,2%</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3315</t>
+          <t>3595</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>4320</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>507</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4539</t>
+          <t>4775</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42150</t>
+          <t>42428</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50512</t>
+          <t>50889</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>48948</t>
+          <t>48776</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55823</t>
+          <t>56315</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>93941</t>
+          <t>94756</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>105170</t>
+          <t>105663</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>93,28%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3874</t>
+          <t>3497</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12236</t>
+          <t>11958</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3063</t>
+          <t>2571</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9938</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>7609</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19331</t>
+          <t>18516</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,35%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43657</t>
+          <t>44305</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51187</t>
+          <t>50768</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>48361</t>
+          <t>47831</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56589</t>
+          <t>56520</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>95321</t>
+          <t>95361</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>106070</t>
+          <t>105859</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>93,97%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9056</t>
+          <t>8408</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3345</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11573</t>
+          <t>12103</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17326</t>
+          <t>17286</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,35%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37496</t>
+          <t>37256</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46144</t>
+          <t>46076</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38488</t>
+          <t>38187</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48779</t>
+          <t>49007</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>79481</t>
+          <t>79386</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>92923</t>
+          <t>92904</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,35%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3536</t>
+          <t>3604</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12184</t>
+          <t>12424</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6693</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16984</t>
+          <t>17285</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12229</t>
+          <t>12248</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25671</t>
+          <t>25766</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,5%</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5428,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12919</t>
+          <t>12360</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16432</t>
+          <t>16601</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22662</t>
+          <t>22655</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32225</t>
+          <t>32209</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39853</t>
+          <t>40043</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,84%</t>
         </is>
       </c>
     </row>
@@ -5546,7 +5546,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5124</t>
+          <t>5683</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8198</t>
+          <t>8029</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2820</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10448</t>
+          <t>10464</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,52%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>36445</t>
+          <t>36451</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>43062</t>
+          <t>43045</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>38057</t>
+          <t>38600</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46242</t>
+          <t>46310</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>78519</t>
+          <t>78203</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>88128</t>
+          <t>88081</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,63%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8097</t>
+          <t>8091</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3291</t>
+          <t>3223</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11476</t>
+          <t>10933</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5947</t>
+          <t>5994</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15556</t>
+          <t>15872</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,87%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>102438</t>
+          <t>102888</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>111932</t>
+          <t>112436</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>102156</t>
+          <t>102108</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>113150</t>
+          <t>113331</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>207917</t>
+          <t>209198</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>222989</t>
+          <t>223327</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,65%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>4268</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14266</t>
+          <t>13816</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8627</t>
+          <t>8446</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>19621</t>
+          <t>19669</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>15491</t>
+          <t>15153</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>30563</t>
+          <t>29282</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>94566</t>
+          <t>94239</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>105949</t>
+          <t>105812</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>106262</t>
+          <t>105915</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>119042</t>
+          <t>119183</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>205248</t>
+          <t>204596</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>222017</t>
+          <t>222395</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,4%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9590</t>
+          <t>9727</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20973</t>
+          <t>21300</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>11426</t>
+          <t>11285</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24206</t>
+          <t>24553</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>23990</t>
+          <t>23612</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>40759</t>
+          <t>41411</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,83%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>417091</t>
+          <t>418324</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>439171</t>
+          <t>438557</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>459598</t>
+          <t>461494</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>485395</t>
+          <t>486339</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>884960</t>
+          <t>884572</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>917749</t>
+          <t>918467</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,42%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>37794</t>
+          <t>38408</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>59874</t>
+          <t>58641</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>53386</t>
+          <t>52442</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>79183</t>
+          <t>77287</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>97997</t>
+          <t>97279</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>130786</t>
+          <t>131174</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,91%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26808</t>
+          <t>26677</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36370</t>
+          <t>36447</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33194</t>
+          <t>33558</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43632</t>
+          <t>43867</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>63431</t>
+          <t>63209</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>77081</t>
+          <t>77680</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,77%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9016</t>
+          <t>8939</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18578</t>
+          <t>18709</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8362</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18800</t>
+          <t>18436</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20299</t>
+          <t>19700</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33949</t>
+          <t>34171</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>35,09%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39409</t>
+          <t>39926</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52678</t>
+          <t>52582</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47754</t>
+          <t>47447</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61215</t>
+          <t>60764</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>91903</t>
+          <t>90828</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>110080</t>
+          <t>110420</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>73,27%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18024</t>
+          <t>18120</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31293</t>
+          <t>30776</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18780</t>
+          <t>19231</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32241</t>
+          <t>32548</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>40617</t>
+          <t>40277</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>58794</t>
+          <t>59869</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>39,73%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30598</t>
+          <t>30997</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43026</t>
+          <t>43753</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32860</t>
+          <t>32424</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45809</t>
+          <t>46088</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>67300</t>
+          <t>67479</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>85077</t>
+          <t>85724</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>68,97%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15087</t>
+          <t>14360</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27515</t>
+          <t>27116</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20368</t>
+          <t>20089</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33317</t>
+          <t>33753</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>39212</t>
+          <t>38565</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>56989</t>
+          <t>56810</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>45,71%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19588</t>
+          <t>18608</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30576</t>
+          <t>30375</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31654</t>
+          <t>31919</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41478</t>
+          <t>41451</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53760</t>
+          <t>54402</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>69170</t>
+          <t>69818</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>75,26%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14537</t>
+          <t>14738</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25525</t>
+          <t>26505</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6172</t>
+          <t>6199</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15996</t>
+          <t>15731</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>23593</t>
+          <t>22945</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39003</t>
+          <t>38361</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>41,35%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25923</t>
+          <t>26420</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31797</t>
+          <t>31804</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31720</t>
+          <t>31737</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>60019</t>
+          <t>60731</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>66612</t>
+          <t>66721</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>571</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6452</t>
+          <t>5955</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3796</t>
+          <t>3779</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8919,7 +8919,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1169</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7871</t>
+          <t>7159</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>10,55%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12435</t>
+          <t>13180</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20735</t>
+          <t>21357</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18505</t>
+          <t>18553</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26809</t>
+          <t>27254</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>34126</t>
+          <t>33936</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>45858</t>
+          <t>46140</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,69%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>5926</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14848</t>
+          <t>14103</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4547</t>
+          <t>4102</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12851</t>
+          <t>12803</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12781</t>
+          <t>12499</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>24513</t>
+          <t>24703</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>42,13%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>66584</t>
+          <t>66140</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>83018</t>
+          <t>82964</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>71300</t>
+          <t>69982</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>87314</t>
+          <t>87712</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>141759</t>
+          <t>142006</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>165704</t>
+          <t>166242</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>70,47%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>33747</t>
+          <t>33801</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>50181</t>
+          <t>50625</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>31809</t>
+          <t>31411</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>47823</t>
+          <t>49141</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>70184</t>
+          <t>69646</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>94129</t>
+          <t>93882</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>39,8%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>114651</t>
+          <t>114461</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>124197</t>
+          <t>124220</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>117571</t>
+          <t>117380</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>129914</t>
+          <t>129255</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>237148</t>
+          <t>236860</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>251892</t>
+          <t>252016</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,73%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5456</t>
+          <t>5433</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>15002</t>
+          <t>15192</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>9309</t>
+          <t>9968</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>21652</t>
+          <t>21843</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>16984</t>
+          <t>16860</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>31728</t>
+          <t>32016</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,91%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>365828</t>
+          <t>367557</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>399645</t>
+          <t>401043</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>69,96%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>415346</t>
+          <t>413730</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>448830</t>
+          <t>448105</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>792992</t>
+          <t>791295</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>837837</t>
+          <t>838073</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>76,44%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>125745</t>
+          <t>124347</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>159562</t>
+          <t>157833</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>122203</t>
+          <t>122928</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>155687</t>
+          <t>157303</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>258586</t>
+          <t>258350</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>303431</t>
+          <t>305128</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,83%</t>
         </is>
       </c>
     </row>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5686</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31526</t>
+          <t>27138</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>3485</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11772</t>
+          <t>11913</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11288</t>
+          <t>11414</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39478</t>
+          <t>38927</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,5%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41756</t>
+          <t>46144</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67596</t>
+          <t>67788</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>67594</t>
+          <t>67453</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>76192</t>
+          <t>75881</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>113170</t>
+          <t>113721</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>141360</t>
+          <t>141234</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,52%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7967</t>
+          <t>7894</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26883</t>
+          <t>27506</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17435</t>
+          <t>17765</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35498</t>
+          <t>34542</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29643</t>
+          <t>29013</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56482</t>
+          <t>55763</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>21,85%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>100771</t>
+          <t>100148</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>119687</t>
+          <t>119760</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>92098</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>110161</t>
+          <t>109831</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>72,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>198768</t>
+          <t>199487</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>225607</t>
+          <t>226237</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,63%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5816</t>
+          <t>5887</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14925</t>
+          <t>14569</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6245</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14439</t>
+          <t>15726</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14383</t>
+          <t>13471</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26771</t>
+          <t>25931</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>20,67%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43343</t>
+          <t>43699</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>52452</t>
+          <t>52381</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52724</t>
+          <t>51437</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60918</t>
+          <t>61042</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>98660</t>
+          <t>99500</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>111048</t>
+          <t>111960</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>89,26%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14446</t>
+          <t>14413</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27891</t>
+          <t>28470</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24377</t>
+          <t>24635</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53178</t>
+          <t>52603</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43147</t>
+          <t>42841</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>76809</t>
+          <t>76791</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>51,79%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>42252</t>
+          <t>41673</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>55697</t>
+          <t>55730</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24956</t>
+          <t>25531</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>53757</t>
+          <t>53499</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>71469</t>
+          <t>71487</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>105131</t>
+          <t>105437</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>71,11%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5281</t>
+          <t>5342</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12628</t>
+          <t>12814</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8803</t>
+          <t>8946</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19078</t>
+          <t>19206</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16425</t>
+          <t>16008</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28431</t>
+          <t>28728</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>38,19%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21885</t>
+          <t>21699</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29232</t>
+          <t>29171</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21641</t>
+          <t>21513</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31916</t>
+          <t>31773</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>46801</t>
+          <t>46504</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>58807</t>
+          <t>59224</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>78,72%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10194</t>
+          <t>9845</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19574</t>
+          <t>19365</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17989</t>
+          <t>17611</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29715</t>
+          <t>28671</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>30727</t>
+          <t>30768</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>45980</t>
+          <t>45524</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>44,48%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>26593</t>
+          <t>26802</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>35973</t>
+          <t>36322</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26471</t>
+          <t>27515</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38575</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>48,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>56373</t>
+          <t>56829</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>71626</t>
+          <t>71585</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>69,94%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4408</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13660</t>
+          <t>13410</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4996</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17622</t>
+          <t>18243</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11226</t>
+          <t>11650</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>26066</t>
+          <t>26371</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>110848</t>
+          <t>111098</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>120100</t>
+          <t>120402</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>138390</t>
+          <t>137769</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>151016</t>
+          <t>150573</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>254454</t>
+          <t>254149</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>269294</t>
+          <t>268870</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,85%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>97263</t>
+          <t>96820</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>113662</t>
+          <t>113659</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>116013</t>
+          <t>116710</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>134562</t>
+          <t>135272</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>219904</t>
+          <t>219767</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>243802</t>
+          <t>243951</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,58%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>17957</t>
+          <t>17960</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>34356</t>
+          <t>34799</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>22233</t>
+          <t>21523</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>40782</t>
+          <t>40085</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>44612</t>
+          <t>44463</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>68510</t>
+          <t>68647</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,8%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>169597</t>
+          <t>169639</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>221165</t>
+          <t>220990</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>227448</t>
+          <t>224471</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>279996</t>
+          <t>283042</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>410914</t>
+          <t>409924</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>491807</t>
+          <t>482981</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>33,82%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>444990</t>
+          <t>445165</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>496558</t>
+          <t>496516</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>481976</t>
+          <t>478930</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>534524</t>
+          <t>537501</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>936320</t>
+          <t>945146</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1017213</t>
+          <t>1018203</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,3%</t>
         </is>
       </c>
     </row>
